--- a/first_model/datasets/dataset_for_first_model.xlsx
+++ b/first_model/datasets/dataset_for_first_model.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1800" windowWidth="19200" windowHeight="6585"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="19200" windowHeight="6585"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2320,6 +2320,9 @@
       <c r="E3" t="s">
         <v>15</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
@@ -2340,7 +2343,7 @@
       <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -2360,7 +2363,7 @@
       <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="H5">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -2400,7 +2403,7 @@
       <c r="E7" t="s">
         <v>26</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1</v>
       </c>
     </row>
@@ -2420,7 +2423,7 @@
       <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1</v>
       </c>
     </row>
@@ -2440,7 +2443,7 @@
       <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="H9">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
@@ -2480,7 +2483,7 @@
       <c r="E11" t="s">
         <v>39</v>
       </c>
-      <c r="H11">
+      <c r="G11">
         <v>1</v>
       </c>
     </row>
@@ -2520,7 +2523,7 @@
       <c r="E13" t="s">
         <v>43</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1</v>
       </c>
     </row>
@@ -2540,7 +2543,7 @@
       <c r="E14" t="s">
         <v>47</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1</v>
       </c>
     </row>
@@ -2580,7 +2583,7 @@
       <c r="E16" t="s">
         <v>51</v>
       </c>
-      <c r="H16">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
@@ -2600,7 +2603,7 @@
       <c r="E17" t="s">
         <v>54</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>1</v>
       </c>
     </row>
@@ -2640,7 +2643,7 @@
       <c r="E19" t="s">
         <v>58</v>
       </c>
-      <c r="H19">
+      <c r="G19">
         <v>1</v>
       </c>
     </row>
@@ -2660,7 +2663,7 @@
       <c r="E20" t="s">
         <v>62</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>1</v>
       </c>
     </row>
@@ -2680,7 +2683,7 @@
       <c r="E21" t="s">
         <v>64</v>
       </c>
-      <c r="H21">
+      <c r="G21">
         <v>1</v>
       </c>
     </row>
@@ -2740,7 +2743,7 @@
       <c r="E24" t="s">
         <v>71</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>1</v>
       </c>
     </row>
@@ -2760,7 +2763,7 @@
       <c r="E25" t="s">
         <v>73</v>
       </c>
-      <c r="H25">
+      <c r="G25">
         <v>1</v>
       </c>
     </row>
@@ -2800,7 +2803,7 @@
       <c r="E27" t="s">
         <v>79</v>
       </c>
-      <c r="H27">
+      <c r="G27">
         <v>1</v>
       </c>
     </row>
@@ -2840,7 +2843,7 @@
       <c r="E29" t="s">
         <v>83</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>1</v>
       </c>
     </row>
@@ -2880,7 +2883,7 @@
       <c r="E31" t="s">
         <v>89</v>
       </c>
-      <c r="H31">
+      <c r="G31">
         <v>1</v>
       </c>
     </row>
@@ -2900,7 +2903,7 @@
       <c r="E32" t="s">
         <v>91</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>1</v>
       </c>
     </row>
@@ -2940,7 +2943,7 @@
       <c r="E34" t="s">
         <v>97</v>
       </c>
-      <c r="H34">
+      <c r="G34">
         <v>1</v>
       </c>
     </row>
@@ -2960,7 +2963,7 @@
       <c r="E35" t="s">
         <v>99</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>1</v>
       </c>
     </row>
@@ -3000,7 +3003,7 @@
       <c r="E37" t="s">
         <v>104</v>
       </c>
-      <c r="H37">
+      <c r="G37">
         <v>1</v>
       </c>
     </row>
@@ -3020,7 +3023,7 @@
       <c r="E38" t="s">
         <v>106</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>1</v>
       </c>
     </row>
@@ -3100,7 +3103,7 @@
       <c r="E42" t="s">
         <v>116</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>1</v>
       </c>
     </row>
@@ -3120,7 +3123,7 @@
       <c r="E43" t="s">
         <v>118</v>
       </c>
-      <c r="H43">
+      <c r="G43">
         <v>1</v>
       </c>
     </row>
@@ -3160,7 +3163,7 @@
       <c r="E45" t="s">
         <v>125</v>
       </c>
-      <c r="H45">
+      <c r="G45">
         <v>1</v>
       </c>
     </row>
@@ -3200,7 +3203,7 @@
       <c r="E47" t="s">
         <v>129</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>1</v>
       </c>
     </row>
@@ -3240,7 +3243,7 @@
       <c r="E49" t="s">
         <v>134</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>1</v>
       </c>
     </row>
@@ -3260,7 +3263,7 @@
       <c r="E50" t="s">
         <v>136</v>
       </c>
-      <c r="H50">
+      <c r="G50">
         <v>1</v>
       </c>
     </row>
@@ -3300,7 +3303,7 @@
       <c r="E52" t="s">
         <v>141</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>1</v>
       </c>
     </row>
@@ -3320,7 +3323,7 @@
       <c r="E53" t="s">
         <v>143</v>
       </c>
-      <c r="H53">
+      <c r="G53">
         <v>1</v>
       </c>
     </row>
@@ -3380,7 +3383,7 @@
       <c r="E56" t="s">
         <v>152</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>1</v>
       </c>
     </row>
@@ -3420,7 +3423,7 @@
       <c r="E58" t="s">
         <v>156</v>
       </c>
-      <c r="H58">
+      <c r="G58">
         <v>1</v>
       </c>
     </row>
@@ -3440,7 +3443,7 @@
       <c r="E59" t="s">
         <v>159</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>1</v>
       </c>
     </row>
@@ -3460,7 +3463,7 @@
       <c r="E60" t="s">
         <v>162</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <v>1</v>
       </c>
     </row>
@@ -3500,7 +3503,7 @@
       <c r="E62" t="s">
         <v>166</v>
       </c>
-      <c r="H62">
+      <c r="G62">
         <v>1</v>
       </c>
     </row>
@@ -3520,7 +3523,7 @@
       <c r="E63" t="s">
         <v>169</v>
       </c>
-      <c r="G63">
+      <c r="H63">
         <v>1</v>
       </c>
     </row>
@@ -3560,7 +3563,7 @@
       <c r="E65" t="s">
         <v>173</v>
       </c>
-      <c r="H65">
+      <c r="G65">
         <v>1</v>
       </c>
     </row>
@@ -3580,7 +3583,7 @@
       <c r="E66" t="s">
         <v>176</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>1</v>
       </c>
     </row>
@@ -3600,7 +3603,7 @@
       <c r="E67" t="s">
         <v>178</v>
       </c>
-      <c r="H67">
+      <c r="G67">
         <v>1</v>
       </c>
     </row>
@@ -3660,7 +3663,7 @@
       <c r="E70" t="s">
         <v>185</v>
       </c>
-      <c r="G70">
+      <c r="H70">
         <v>1</v>
       </c>
     </row>
@@ -3680,7 +3683,7 @@
       <c r="E71" t="s">
         <v>188</v>
       </c>
-      <c r="H71">
+      <c r="G71">
         <v>1</v>
       </c>
     </row>
@@ -3700,7 +3703,7 @@
       <c r="E72" t="s">
         <v>191</v>
       </c>
-      <c r="G72">
+      <c r="H72">
         <v>1</v>
       </c>
     </row>
@@ -3740,7 +3743,7 @@
       <c r="E74" t="s">
         <v>195</v>
       </c>
-      <c r="H74">
+      <c r="G74">
         <v>1</v>
       </c>
     </row>
@@ -3760,7 +3763,7 @@
       <c r="E75" t="s">
         <v>198</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>1</v>
       </c>
     </row>
@@ -3840,7 +3843,7 @@
       <c r="E79" t="s">
         <v>208</v>
       </c>
-      <c r="G79">
+      <c r="H79">
         <v>1</v>
       </c>
     </row>
@@ -3860,7 +3863,7 @@
       <c r="E80" t="s">
         <v>210</v>
       </c>
-      <c r="H80">
+      <c r="G80">
         <v>1</v>
       </c>
     </row>
@@ -3920,7 +3923,7 @@
       <c r="E83" t="s">
         <v>218</v>
       </c>
-      <c r="H83">
+      <c r="G83">
         <v>1</v>
       </c>
     </row>
@@ -3940,7 +3943,7 @@
       <c r="E84" t="s">
         <v>220</v>
       </c>
-      <c r="G84">
+      <c r="H84">
         <v>1</v>
       </c>
     </row>
@@ -3960,7 +3963,7 @@
       <c r="E85" t="s">
         <v>223</v>
       </c>
-      <c r="G85">
+      <c r="H85">
         <v>1</v>
       </c>
     </row>
@@ -3980,7 +3983,7 @@
       <c r="E86" t="s">
         <v>225</v>
       </c>
-      <c r="H86">
+      <c r="G86">
         <v>1</v>
       </c>
     </row>
@@ -4020,7 +4023,7 @@
       <c r="E88" t="s">
         <v>231</v>
       </c>
-      <c r="H88">
+      <c r="G88">
         <v>1</v>
       </c>
     </row>
@@ -4040,7 +4043,7 @@
       <c r="E89" t="s">
         <v>233</v>
       </c>
-      <c r="G89">
+      <c r="H89">
         <v>1</v>
       </c>
     </row>
@@ -4100,7 +4103,7 @@
       <c r="E92" t="s">
         <v>240</v>
       </c>
-      <c r="G92">
+      <c r="H92">
         <v>1</v>
       </c>
     </row>
@@ -4120,7 +4123,7 @@
       <c r="E93" t="s">
         <v>242</v>
       </c>
-      <c r="H93">
+      <c r="G93">
         <v>1</v>
       </c>
     </row>
@@ -4160,7 +4163,7 @@
       <c r="E95" t="s">
         <v>247</v>
       </c>
-      <c r="G95">
+      <c r="H95">
         <v>1</v>
       </c>
     </row>
@@ -4180,7 +4183,7 @@
       <c r="E96" t="s">
         <v>249</v>
       </c>
-      <c r="H96">
+      <c r="G96">
         <v>1</v>
       </c>
     </row>
@@ -4200,7 +4203,7 @@
       <c r="E97" t="s">
         <v>252</v>
       </c>
-      <c r="G97">
+      <c r="H97">
         <v>1</v>
       </c>
     </row>
@@ -4240,7 +4243,7 @@
       <c r="E99" t="s">
         <v>256</v>
       </c>
-      <c r="H99">
+      <c r="G99">
         <v>1</v>
       </c>
     </row>
@@ -4260,7 +4263,7 @@
       <c r="E100" t="s">
         <v>259</v>
       </c>
-      <c r="H100">
+      <c r="G100">
         <v>1</v>
       </c>
     </row>
@@ -4280,7 +4283,7 @@
       <c r="E101" t="s">
         <v>261</v>
       </c>
-      <c r="G101">
+      <c r="H101">
         <v>1</v>
       </c>
     </row>
@@ -4340,7 +4343,7 @@
       <c r="E104" t="s">
         <v>268</v>
       </c>
-      <c r="H104">
+      <c r="G104">
         <v>1</v>
       </c>
     </row>
@@ -4360,7 +4363,7 @@
       <c r="E105" t="s">
         <v>270</v>
       </c>
-      <c r="G105">
+      <c r="H105">
         <v>1</v>
       </c>
     </row>
@@ -4400,7 +4403,7 @@
       <c r="E107" t="s">
         <v>277</v>
       </c>
-      <c r="H107">
+      <c r="G107">
         <v>1</v>
       </c>
     </row>
@@ -4440,7 +4443,7 @@
       <c r="E109" t="s">
         <v>281</v>
       </c>
-      <c r="G109">
+      <c r="H109">
         <v>1</v>
       </c>
     </row>
@@ -4480,7 +4483,7 @@
       <c r="E111" t="s">
         <v>287</v>
       </c>
-      <c r="H111">
+      <c r="G111">
         <v>1</v>
       </c>
     </row>
@@ -4520,7 +4523,7 @@
       <c r="E113" t="s">
         <v>291</v>
       </c>
-      <c r="G113">
+      <c r="H113">
         <v>1</v>
       </c>
     </row>
@@ -4540,7 +4543,7 @@
       <c r="E114" t="s">
         <v>294</v>
       </c>
-      <c r="H114">
+      <c r="G114">
         <v>1</v>
       </c>
     </row>
@@ -4560,7 +4563,7 @@
       <c r="E115" t="s">
         <v>296</v>
       </c>
-      <c r="G115">
+      <c r="H115">
         <v>1</v>
       </c>
     </row>
@@ -4600,7 +4603,7 @@
       <c r="E117" t="s">
         <v>301</v>
       </c>
-      <c r="G117">
+      <c r="H117">
         <v>1</v>
       </c>
     </row>
@@ -4640,7 +4643,7 @@
       <c r="E119" t="s">
         <v>306</v>
       </c>
-      <c r="H119">
+      <c r="G119">
         <v>1</v>
       </c>
     </row>
@@ -4660,7 +4663,7 @@
       <c r="E120" t="s">
         <v>308</v>
       </c>
-      <c r="G120">
+      <c r="H120">
         <v>1</v>
       </c>
     </row>
@@ -4720,7 +4723,7 @@
       <c r="E123" t="s">
         <v>316</v>
       </c>
-      <c r="H123">
+      <c r="G123">
         <v>1</v>
       </c>
     </row>
@@ -4740,7 +4743,7 @@
       <c r="E124" t="s">
         <v>318</v>
       </c>
-      <c r="G124">
+      <c r="H124">
         <v>1</v>
       </c>
     </row>
@@ -4760,7 +4763,7 @@
       <c r="E125" t="s">
         <v>321</v>
       </c>
-      <c r="G125">
+      <c r="H125">
         <v>1</v>
       </c>
     </row>
@@ -4800,7 +4803,7 @@
       <c r="E127" t="s">
         <v>325</v>
       </c>
-      <c r="H127">
+      <c r="G127">
         <v>1</v>
       </c>
     </row>
@@ -4860,7 +4863,7 @@
       <c r="E130" t="s">
         <v>333</v>
       </c>
-      <c r="H130">
+      <c r="G130">
         <v>1</v>
       </c>
     </row>
@@ -4880,7 +4883,7 @@
       <c r="E131" t="s">
         <v>335</v>
       </c>
-      <c r="G131">
+      <c r="H131">
         <v>1</v>
       </c>
     </row>
@@ -4920,7 +4923,7 @@
       <c r="E133" t="s">
         <v>340</v>
       </c>
-      <c r="G133">
+      <c r="H133">
         <v>1</v>
       </c>
     </row>
@@ -4940,7 +4943,7 @@
       <c r="E134" t="s">
         <v>343</v>
       </c>
-      <c r="H134">
+      <c r="G134">
         <v>1</v>
       </c>
     </row>
@@ -4980,7 +4983,7 @@
       <c r="E136" t="s">
         <v>347</v>
       </c>
-      <c r="G136">
+      <c r="H136">
         <v>1</v>
       </c>
     </row>
@@ -5000,7 +5003,7 @@
       <c r="E137" t="s">
         <v>350</v>
       </c>
-      <c r="H137">
+      <c r="G137">
         <v>1</v>
       </c>
     </row>
@@ -5040,7 +5043,7 @@
       <c r="E139" t="s">
         <v>354</v>
       </c>
-      <c r="G139">
+      <c r="H139">
         <v>1</v>
       </c>
     </row>
@@ -5080,7 +5083,7 @@
       <c r="E141" t="s">
         <v>359</v>
       </c>
-      <c r="H141">
+      <c r="G141">
         <v>1</v>
       </c>
     </row>
@@ -5100,7 +5103,7 @@
       <c r="E142" t="s">
         <v>361</v>
       </c>
-      <c r="G142">
+      <c r="H142">
         <v>1</v>
       </c>
     </row>
@@ -5120,7 +5123,7 @@
       <c r="E143" t="s">
         <v>364</v>
       </c>
-      <c r="G143">
+      <c r="H143">
         <v>1</v>
       </c>
     </row>
@@ -5160,7 +5163,7 @@
       <c r="E145" t="s">
         <v>368</v>
       </c>
-      <c r="H145">
+      <c r="G145">
         <v>1</v>
       </c>
     </row>
@@ -5180,7 +5183,7 @@
       <c r="E146" t="s">
         <v>371</v>
       </c>
-      <c r="G146">
+      <c r="H146">
         <v>1</v>
       </c>
     </row>
@@ -5220,7 +5223,7 @@
       <c r="E148" t="s">
         <v>375</v>
       </c>
-      <c r="H148">
+      <c r="G148">
         <v>1</v>
       </c>
     </row>
@@ -5260,7 +5263,7 @@
       <c r="E150" t="s">
         <v>381</v>
       </c>
-      <c r="G150">
+      <c r="H150">
         <v>1</v>
       </c>
     </row>
@@ -5280,7 +5283,7 @@
       <c r="E151" t="s">
         <v>383</v>
       </c>
-      <c r="H151">
+      <c r="G151">
         <v>1</v>
       </c>
     </row>
@@ -5340,7 +5343,7 @@
       <c r="E154" t="s">
         <v>390</v>
       </c>
-      <c r="G154">
+      <c r="H154">
         <v>1</v>
       </c>
     </row>
@@ -5360,7 +5363,7 @@
       <c r="E155" t="s">
         <v>392</v>
       </c>
-      <c r="H155">
+      <c r="G155">
         <v>1</v>
       </c>
     </row>
@@ -5380,7 +5383,7 @@
       <c r="E156" t="s">
         <v>395</v>
       </c>
-      <c r="G156">
+      <c r="H156">
         <v>1</v>
       </c>
     </row>
@@ -5400,7 +5403,7 @@
       <c r="E157" t="s">
         <v>397</v>
       </c>
-      <c r="H157">
+      <c r="G157">
         <v>1</v>
       </c>
     </row>
@@ -5440,7 +5443,7 @@
       <c r="E159" t="s">
         <v>403</v>
       </c>
-      <c r="G159">
+      <c r="H159">
         <v>1</v>
       </c>
     </row>
@@ -5480,7 +5483,7 @@
       <c r="E161" t="s">
         <v>407</v>
       </c>
-      <c r="H161">
+      <c r="G161">
         <v>1</v>
       </c>
     </row>
@@ -5520,7 +5523,7 @@
       <c r="E163" t="s">
         <v>412</v>
       </c>
-      <c r="G163">
+      <c r="H163">
         <v>1</v>
       </c>
     </row>
@@ -5540,7 +5543,7 @@
       <c r="E164" t="s">
         <v>415</v>
       </c>
-      <c r="G164">
+      <c r="H164">
         <v>1</v>
       </c>
     </row>
@@ -5580,7 +5583,7 @@
       <c r="E166" t="s">
         <v>419</v>
       </c>
-      <c r="H166">
+      <c r="G166">
         <v>1</v>
       </c>
     </row>
@@ -5600,7 +5603,7 @@
       <c r="E167" t="s">
         <v>422</v>
       </c>
-      <c r="G167">
+      <c r="H167">
         <v>1</v>
       </c>
     </row>
@@ -5620,7 +5623,7 @@
       <c r="E168" t="s">
         <v>424</v>
       </c>
-      <c r="H168">
+      <c r="G168">
         <v>1</v>
       </c>
     </row>
@@ -5680,7 +5683,7 @@
       <c r="E171" t="s">
         <v>432</v>
       </c>
-      <c r="H171">
+      <c r="G171">
         <v>1</v>
       </c>
     </row>
@@ -5720,7 +5723,7 @@
       <c r="E173" t="s">
         <v>436</v>
       </c>
-      <c r="G173">
+      <c r="H173">
         <v>1</v>
       </c>
     </row>
@@ -5740,7 +5743,7 @@
       <c r="E174" t="s">
         <v>439</v>
       </c>
-      <c r="G174">
+      <c r="H174">
         <v>1</v>
       </c>
     </row>
@@ -5760,7 +5763,7 @@
       <c r="E175" t="s">
         <v>441</v>
       </c>
-      <c r="H175">
+      <c r="G175">
         <v>1</v>
       </c>
     </row>
@@ -5800,7 +5803,7 @@
       <c r="E177" t="s">
         <v>446</v>
       </c>
-      <c r="H177">
+      <c r="G177">
         <v>1</v>
       </c>
     </row>
@@ -5840,7 +5843,7 @@
       <c r="E179" t="s">
         <v>450</v>
       </c>
-      <c r="G179">
+      <c r="H179">
         <v>1</v>
       </c>
     </row>
@@ -5880,7 +5883,7 @@
       <c r="E181" t="s">
         <v>456</v>
       </c>
-      <c r="H181">
+      <c r="G181">
         <v>1</v>
       </c>
     </row>
@@ -5920,7 +5923,7 @@
       <c r="E183" t="s">
         <v>460</v>
       </c>
-      <c r="G183">
+      <c r="H183">
         <v>1</v>
       </c>
     </row>
@@ -5960,7 +5963,7 @@
       <c r="E185" t="s">
         <v>465</v>
       </c>
-      <c r="H185">
+      <c r="G185">
         <v>1</v>
       </c>
     </row>
@@ -5980,7 +5983,7 @@
       <c r="E186" t="s">
         <v>467</v>
       </c>
-      <c r="G186">
+      <c r="H186">
         <v>1</v>
       </c>
     </row>
@@ -6000,7 +6003,7 @@
       <c r="E187" t="s">
         <v>470</v>
       </c>
-      <c r="H187">
+      <c r="G187">
         <v>1</v>
       </c>
     </row>
@@ -6020,7 +6023,7 @@
       <c r="E188" t="s">
         <v>472</v>
       </c>
-      <c r="G188">
+      <c r="H188">
         <v>1</v>
       </c>
     </row>
@@ -6060,7 +6063,7 @@
       <c r="E190" t="s">
         <v>477</v>
       </c>
-      <c r="H190">
+      <c r="G190">
         <v>1</v>
       </c>
     </row>
@@ -6100,7 +6103,7 @@
       <c r="E192" t="s">
         <v>481</v>
       </c>
-      <c r="G192">
+      <c r="H192">
         <v>1</v>
       </c>
     </row>
@@ -6120,7 +6123,7 @@
       <c r="E193" t="s">
         <v>484</v>
       </c>
-      <c r="H193">
+      <c r="G193">
         <v>1</v>
       </c>
     </row>
@@ -6160,7 +6163,7 @@
       <c r="E195" t="s">
         <v>488</v>
       </c>
-      <c r="G195">
+      <c r="H195">
         <v>1</v>
       </c>
     </row>
@@ -6220,7 +6223,7 @@
       <c r="E198" t="s">
         <v>496</v>
       </c>
-      <c r="H198">
+      <c r="G198">
         <v>1</v>
       </c>
     </row>
@@ -6240,7 +6243,7 @@
       <c r="E199" t="s">
         <v>498</v>
       </c>
-      <c r="G199">
+      <c r="H199">
         <v>1</v>
       </c>
     </row>
@@ -6280,7 +6283,7 @@
       <c r="E201" t="s">
         <v>503</v>
       </c>
-      <c r="G201">
+      <c r="H201">
         <v>1</v>
       </c>
     </row>
@@ -6300,7 +6303,7 @@
       <c r="E202" t="s">
         <v>505</v>
       </c>
-      <c r="H202">
+      <c r="G202">
         <v>1</v>
       </c>
     </row>
@@ -6320,7 +6323,7 @@
       <c r="E203" t="s">
         <v>508</v>
       </c>
-      <c r="H203">
+      <c r="G203">
         <v>1</v>
       </c>
     </row>
@@ -6340,7 +6343,7 @@
       <c r="E204" t="s">
         <v>510</v>
       </c>
-      <c r="G204">
+      <c r="H204">
         <v>1</v>
       </c>
     </row>
@@ -6420,7 +6423,7 @@
       <c r="E208" t="s">
         <v>521</v>
       </c>
-      <c r="H208">
+      <c r="G208">
         <v>1</v>
       </c>
     </row>
@@ -6460,7 +6463,7 @@
       <c r="E210" t="s">
         <v>525</v>
       </c>
-      <c r="G210">
+      <c r="H210">
         <v>1</v>
       </c>
     </row>
@@ -6480,7 +6483,7 @@
       <c r="E211" t="s">
         <v>528</v>
       </c>
-      <c r="G211">
+      <c r="H211">
         <v>1</v>
       </c>
     </row>
@@ -6500,7 +6503,7 @@
       <c r="E212" t="s">
         <v>530</v>
       </c>
-      <c r="H212">
+      <c r="G212">
         <v>1</v>
       </c>
     </row>
@@ -6560,7 +6563,7 @@
       <c r="E215" t="s">
         <v>537</v>
       </c>
-      <c r="G215">
+      <c r="H215">
         <v>1</v>
       </c>
     </row>
@@ -6580,7 +6583,7 @@
       <c r="E216" t="s">
         <v>539</v>
       </c>
-      <c r="H216">
+      <c r="G216">
         <v>1</v>
       </c>
     </row>
@@ -6600,7 +6603,7 @@
       <c r="E217" t="s">
         <v>542</v>
       </c>
-      <c r="H217">
+      <c r="G217">
         <v>1</v>
       </c>
     </row>
@@ -6620,7 +6623,7 @@
       <c r="E218" t="s">
         <v>544</v>
       </c>
-      <c r="G218">
+      <c r="H218">
         <v>1</v>
       </c>
     </row>
@@ -6660,7 +6663,7 @@
       <c r="E220" t="s">
         <v>549</v>
       </c>
-      <c r="H220">
+      <c r="G220">
         <v>1</v>
       </c>
     </row>
@@ -6680,7 +6683,7 @@
       <c r="E221" t="s">
         <v>551</v>
       </c>
-      <c r="G221">
+      <c r="H221">
         <v>1</v>
       </c>
     </row>
@@ -6740,7 +6743,7 @@
       <c r="E224" t="s">
         <v>559</v>
       </c>
-      <c r="H224">
+      <c r="G224">
         <v>1</v>
       </c>
     </row>
@@ -6760,7 +6763,7 @@
       <c r="E225" t="s">
         <v>561</v>
       </c>
-      <c r="G225">
+      <c r="H225">
         <v>1</v>
       </c>
     </row>
@@ -6840,7 +6843,7 @@
       <c r="E229" t="s">
         <v>572</v>
       </c>
-      <c r="H229">
+      <c r="G229">
         <v>1</v>
       </c>
     </row>
@@ -6860,7 +6863,7 @@
       <c r="E230" t="s">
         <v>574</v>
       </c>
-      <c r="G230">
+      <c r="H230">
         <v>1</v>
       </c>
     </row>
@@ -6900,7 +6903,7 @@
       <c r="E232" t="s">
         <v>579</v>
       </c>
-      <c r="G232">
+      <c r="H232">
         <v>1</v>
       </c>
     </row>
@@ -6920,7 +6923,7 @@
       <c r="E233" t="s">
         <v>581</v>
       </c>
-      <c r="H233">
+      <c r="G233">
         <v>1</v>
       </c>
     </row>
@@ -6960,7 +6963,7 @@
       <c r="E235" t="s">
         <v>586</v>
       </c>
-      <c r="G235">
+      <c r="H235">
         <v>1</v>
       </c>
     </row>
@@ -6980,7 +6983,7 @@
       <c r="E236" t="s">
         <v>588</v>
       </c>
-      <c r="H236">
+      <c r="G236">
         <v>1</v>
       </c>
     </row>
@@ -7020,7 +7023,7 @@
       <c r="E238" t="s">
         <v>593</v>
       </c>
-      <c r="H238">
+      <c r="G238">
         <v>1</v>
       </c>
     </row>
@@ -7060,7 +7063,7 @@
       <c r="E240" t="s">
         <v>597</v>
       </c>
-      <c r="G240">
+      <c r="H240">
         <v>1</v>
       </c>
     </row>
@@ -7080,7 +7083,7 @@
       <c r="E241" t="s">
         <v>600</v>
       </c>
-      <c r="G241">
+      <c r="H241">
         <v>1</v>
       </c>
     </row>
@@ -7100,7 +7103,7 @@
       <c r="E242" t="s">
         <v>602</v>
       </c>
-      <c r="H242">
+      <c r="G242">
         <v>1</v>
       </c>
     </row>
@@ -7140,7 +7143,7 @@
       <c r="E244" t="s">
         <v>607</v>
       </c>
-      <c r="G244">
+      <c r="H244">
         <v>1</v>
       </c>
     </row>
@@ -7180,7 +7183,7 @@
       <c r="E246" t="s">
         <v>611</v>
       </c>
-      <c r="H246">
+      <c r="G246">
         <v>1</v>
       </c>
     </row>
@@ -7220,7 +7223,7 @@
       <c r="E248" t="s">
         <v>617</v>
       </c>
-      <c r="G248">
+      <c r="H248">
         <v>1</v>
       </c>
     </row>
@@ -7260,7 +7263,7 @@
       <c r="E250" t="s">
         <v>621</v>
       </c>
-      <c r="H250">
+      <c r="G250">
         <v>1</v>
       </c>
     </row>
@@ -7280,7 +7283,7 @@
       <c r="E251" t="s">
         <v>624</v>
       </c>
-      <c r="G251">
+      <c r="H251">
         <v>1</v>
       </c>
     </row>
@@ -7300,7 +7303,7 @@
       <c r="E252" t="s">
         <v>626</v>
       </c>
-      <c r="H252">
+      <c r="G252">
         <v>1</v>
       </c>
     </row>

--- a/first_model/datasets/dataset_for_first_model.xlsx
+++ b/first_model/datasets/dataset_for_first_model.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2400" windowWidth="19200" windowHeight="6585"/>
+    <workbookView xWindow="0" yWindow="3000" windowWidth="19200" windowHeight="6585"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2323,9 +2323,6 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
